--- a/artfynd/A 72588-2021 artfynd.xlsx
+++ b/artfynd/A 72588-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72588-2021 artfynd.xlsx
+++ b/artfynd/A 72588-2021 artfynd.xlsx
@@ -675,62 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87951307</v>
+        <v>99585501</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ödalen, 250 m åt ONO, Boh</t>
+          <t>Ölseröd, Henån, Orust, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>306142.3908669791</v>
+        <v>306016</v>
       </c>
       <c r="R2" t="n">
-        <v>6457726.141897568</v>
+        <v>6458017</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,34 +754,14 @@
           <t>Röra</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>OB-Oru-1839</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>bladrosetter avses. 9 blommande</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,89 +770,75 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
+          <t>Peter Nielsen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Molander</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Peter Nielsen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99585501</v>
+        <v>103317134</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Roth</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ölseröd, Henån, Orust, Boh</t>
+          <t>Ödalen, 150m O, Henån, Orust, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>306016.0297836399</v>
+        <v>306167</v>
       </c>
       <c r="R3" t="n">
-        <v>6458016.730868652</v>
+        <v>6457608</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,22 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,60 +879,56 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Peter Nielsen</t>
+          <t>Jenny Eikestam</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Nielsen</t>
+          <t>Jenny Eikestam</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103317134</v>
+        <v>87951307</v>
       </c>
       <c r="B4" t="n">
-        <v>95717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -990,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ödalen, 150m O, Henån, Orust, Boh</t>
+          <t>Ödalen, 250 m åt ONO, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306167.8293905949</v>
+        <v>306142</v>
       </c>
       <c r="R4" t="n">
-        <v>6457608.810858846</v>
+        <v>6457726</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1022,24 +973,24 @@
           <t>Röra</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>OB-Oru-1839</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>bladrosetter avses. 9 blommande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,15 +1006,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jenny Eikestam</t>
+          <t>Olle Molander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenny Eikestam</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Olle Molander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 72588-2021 artfynd.xlsx
+++ b/artfynd/A 72588-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99585501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103317134</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,8 +1034,18 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87951307</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>